--- a/docs/TitanOS_Pricing_Calculator.xlsx
+++ b/docs/TitanOS_Pricing_Calculator.xlsx
@@ -106,7 +106,7 @@
     <t xml:space="preserve">Core</t>
   </si>
   <si>
-    <t xml:space="preserve">Private</t>
+    <t xml:space="preserve">Premier</t>
   </si>
   <si>
     <t xml:space="preserve">Estate</t>
